--- a/InputData/land/RPEpUACE/Rebound Pol Emis per Unit Avoided CO2 Emis.xlsx
+++ b/InputData/land/RPEpUACE/Rebound Pol Emis per Unit Avoided CO2 Emis.xlsx
@@ -1,27 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28619"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\land\RPEpUACE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skorpius/My Drive/2024/FO local_EPS ICM/Diario/20250226_CATCHUP/land_CPL/RPEpUACE/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DAEEDE-B0CE-AD4E-B751-A1E19CC79CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="383" yWindow="83" windowWidth="19140" windowHeight="9263"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="RPEpUACE" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="64">
   <si>
     <t>RPEpUACE Rebound Pollutant Emissions per Unit Avoided CO2 Emissions</t>
   </si>
@@ -29,10 +46,16 @@
     <t>Source:</t>
   </si>
   <si>
-    <t>http://www.epa.gov/climatechange/Downloads/ghgemissions/US-GHG-Inventory-2015-Main-Text.pdf</t>
-  </si>
-  <si>
-    <t>Page 6-4, Table 6-3</t>
+    <t>US EPA</t>
+  </si>
+  <si>
+    <t>Inventory of US Greenhouse Gas Emissions Emissions and Sinks: 1990-2020</t>
+  </si>
+  <si>
+    <t>https://www.epa.gov/ghgemissions/inventory-us-greenhouse-gas-emissions-and-sinks-1990-2020</t>
+  </si>
+  <si>
+    <t>Table 6-3</t>
   </si>
   <si>
     <t>Notes</t>
@@ -53,30 +76,135 @@
     <t>and to the effects of policy levers in the model.</t>
   </si>
   <si>
-    <t>U.S. EPA</t>
-  </si>
-  <si>
-    <t>Excerpt from Table 6-3:</t>
+    <t>Mexico Notes</t>
+  </si>
+  <si>
+    <t>No specific data for Mexico available.</t>
+  </si>
+  <si>
+    <t>Latest US EPA data used.</t>
+  </si>
+  <si>
+    <t>Table 6-3:</t>
+  </si>
+  <si>
+    <t>Unit: kt</t>
+  </si>
+  <si>
+    <t>Table 6-3:  Emissions and Removals from Land Use, Land-Use Change, and Forestry by Gas (kt)</t>
+  </si>
+  <si>
+    <t>Gas/Land-Use Category</t>
+  </si>
+  <si>
+    <t>Carbon Stock Change (CO2)a</t>
+  </si>
+  <si>
+    <t>Forest Land Remaining Forest Land</t>
+  </si>
+  <si>
+    <t>Land Converted to Forest Land</t>
+  </si>
+  <si>
+    <t>Cropland Remaining Cropland</t>
+  </si>
+  <si>
+    <t>Land Converted to Cropland</t>
+  </si>
+  <si>
+    <t>Grassland Remaining Grassland</t>
+  </si>
+  <si>
+    <t>Land Converted to Grassland</t>
+  </si>
+  <si>
+    <t>Wetlands Remaining Wetlands</t>
+  </si>
+  <si>
+    <t>Land Converted to Wetlands</t>
+  </si>
+  <si>
+    <t>Settlements Remaining Settlements</t>
+  </si>
+  <si>
+    <t>Land Converted to Settlements</t>
+  </si>
+  <si>
+    <t>CH4</t>
+  </si>
+  <si>
+    <t>Forest Land Remaining Forest Land: Forest Firesb</t>
+  </si>
+  <si>
+    <t>Forest Land Remaining Forest Land: Drained Organic Soilsd</t>
+  </si>
+  <si>
+    <t>Grassland Remaining Grassland: Grassland Firesc</t>
+  </si>
+  <si>
+    <t>Wetlands Remaining Wetlands: Flooded Land Remaining Flooded Land</t>
+  </si>
+  <si>
+    <t>Wetlands Remaining Wetlands: Coastal Wetlands Remaining Coastal Wetlands</t>
+  </si>
+  <si>
+    <t>Wetlands Remaining Wetlands: Peatlands Remaining Peatlands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ </t>
+  </si>
+  <si>
+    <t>Land Converted to Wetlands: Land Converted to Flooded Lands</t>
+  </si>
+  <si>
+    <t>Land Converted to Wetlands: Land Converted to Coastal Wetlands</t>
+  </si>
+  <si>
+    <t>N2O</t>
+  </si>
+  <si>
+    <t>Forest Land Remaining Forest Land: Forest Soilsf</t>
+  </si>
+  <si>
+    <t>Settlements Remaining Settlements: Settlement Soilse</t>
+  </si>
+  <si>
+    <t>+ Absolute value does not exceed 0.5 kt.</t>
+  </si>
+  <si>
+    <t>a LULUCF Carbon Stock Change is the net C stock change from the following categories: Forest Land Remaining Forest Land, Land Converted to Forest Land, Cropland Remaining Cropland, Land Converted to Cropland, Grassland Remaining Grassland, Land Converted to Grassland, Wetlands Remaining Wetlands, Land Converted to Wetlands, Settlements Remaining Settlements, and Land Converted to Settlements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b Estimates include CH4 and N2O emissions from fires on both Forest Land Remaining Forest Land and Land Converted to Forest Land. </t>
+  </si>
+  <si>
+    <t>c Estimates include CH4 and N2O emissions from drained organic soils on both Forest Land Remaining Forest Land and Land Converted to Forest Land.</t>
+  </si>
+  <si>
+    <t>d Estimates include CH4 and N2O emissions from fires on both Grassland Remaining Grassland and Land Converted to Grassland.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e Estimates include N2O emissions from N fertilizer additions on both Forest Land Remaining Forest Land and Land Converted to Forest Land. </t>
+  </si>
+  <si>
+    <t>f Estimates include N2O emissions from N fertilizer additions on both Settlements Remaining Settlements and Land Converted to Settlements.</t>
+  </si>
+  <si>
+    <t>Notes: Totals may not sum due to independent rounding. Parentheses indicate net sequestration.</t>
+  </si>
+  <si>
+    <t>CH4/CO2 Ratio</t>
+  </si>
+  <si>
+    <t>N2O/CO2 Ratio</t>
+  </si>
+  <si>
+    <t>Rebound Emis Factor (dimensionless)</t>
   </si>
   <si>
     <t>CO2</t>
   </si>
   <si>
-    <t>CH4</t>
-  </si>
-  <si>
-    <t>N2O</t>
-  </si>
-  <si>
-    <t>Unit: kt</t>
-  </si>
-  <si>
-    <t>CH4/CO2 Ratio</t>
-  </si>
-  <si>
-    <t>N2O/CO2 Ratio</t>
-  </si>
-  <si>
     <t>VOC</t>
   </si>
   <si>
@@ -102,19 +230,13 @@
   </si>
   <si>
     <t>F gases</t>
-  </si>
-  <si>
-    <t>Inventory of U.S. Greenhouse Gas Emissions and Sinks: 1990-2013</t>
-  </si>
-  <si>
-    <t>Rebound Emis Factor (dimensionless)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,7 +282,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -168,6 +290,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -187,9 +310,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -227,9 +350,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -264,7 +387,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -299,7 +422,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -472,226 +595,786 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="B4" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="B6" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B4" s="4">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B6" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.19921875" customWidth="1"/>
-    <col min="2" max="2" width="8.86328125" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>2016</v>
+      </c>
+      <c r="C4">
+        <v>2017</v>
+      </c>
+      <c r="D4">
+        <v>2018</v>
+      </c>
+      <c r="E4">
+        <v>2019</v>
+      </c>
+      <c r="F4">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>-862045</v>
+      </c>
+      <c r="C5" s="5">
+        <v>-826667</v>
+      </c>
+      <c r="D5" s="5">
+        <v>-809026</v>
+      </c>
+      <c r="E5" s="5">
+        <v>-760820</v>
+      </c>
+      <c r="F5" s="5">
+        <v>-812176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>-725571</v>
+      </c>
+      <c r="C6" s="5">
+        <v>-688301</v>
+      </c>
+      <c r="D6" s="5">
+        <v>-677101</v>
+      </c>
+      <c r="E6" s="5">
+        <v>-634824</v>
+      </c>
+      <c r="F6" s="5">
+        <v>-668057</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>-99454</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-99523</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-99518</v>
+      </c>
+      <c r="E7" s="5">
+        <v>-99520</v>
+      </c>
+      <c r="F7" s="5">
+        <v>-99521</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>-22731</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-22293</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-16597</v>
+      </c>
+      <c r="E8" s="5">
+        <v>-14544</v>
+      </c>
+      <c r="F8" s="5">
+        <v>-23335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>54107</v>
+      </c>
+      <c r="C9" s="5">
+        <v>54273</v>
+      </c>
+      <c r="D9" s="5">
+        <v>53975</v>
+      </c>
+      <c r="E9" s="5">
+        <v>53935</v>
+      </c>
+      <c r="F9" s="5">
+        <v>54380</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>7958</v>
+      </c>
+      <c r="C10" s="5">
+        <v>9308</v>
+      </c>
+      <c r="D10" s="5">
+        <v>9670</v>
+      </c>
+      <c r="E10" s="5">
+        <v>12425</v>
+      </c>
+      <c r="F10" s="5">
+        <v>4497</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>-22553</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-22693</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-22397</v>
+      </c>
+      <c r="E11" s="5">
+        <v>-21485</v>
+      </c>
+      <c r="F11" s="5">
+        <v>-24101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>-8046</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-7954</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-7994</v>
+      </c>
+      <c r="E12" s="5">
+        <v>-8034</v>
+      </c>
+      <c r="F12" s="5">
+        <v>-8084</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13">
+        <v>254</v>
+      </c>
+      <c r="C13">
+        <v>258</v>
+      </c>
+      <c r="D13">
+        <v>265</v>
+      </c>
+      <c r="E13">
+        <v>271</v>
+      </c>
+      <c r="F13">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>-123794</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-127679</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-127299</v>
+      </c>
+      <c r="E14" s="5">
+        <v>-126977</v>
+      </c>
+      <c r="F14" s="5">
+        <v>-126128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>77784</v>
+      </c>
+      <c r="C15" s="5">
+        <v>77938</v>
+      </c>
+      <c r="D15" s="5">
+        <v>77970</v>
+      </c>
+      <c r="E15" s="5">
+        <v>77932</v>
+      </c>
+      <c r="F15" s="5">
+        <v>77895</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1131</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1359</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1226</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1022</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17">
+        <v>154</v>
+      </c>
+      <c r="C17">
+        <v>381</v>
+      </c>
+      <c r="D17">
+        <v>249</v>
+      </c>
+      <c r="E17">
+        <v>45</v>
+      </c>
+      <c r="F17">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B3">
-        <v>2009</v>
-      </c>
-      <c r="C3">
-        <v>2010</v>
-      </c>
-      <c r="D3">
-        <v>2011</v>
-      </c>
-      <c r="E3">
-        <v>2012</v>
-      </c>
-      <c r="F3">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="C19">
         <v>12</v>
       </c>
-      <c r="B4">
-        <v>-862631</v>
-      </c>
-      <c r="C4">
-        <v>-862025</v>
-      </c>
-      <c r="D4">
-        <v>-872103</v>
-      </c>
-      <c r="E4">
-        <v>-869580</v>
-      </c>
-      <c r="F4">
-        <v>-871026</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="D19">
+        <v>12</v>
+      </c>
+      <c r="E19">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20">
+        <v>796.7</v>
+      </c>
+      <c r="C20">
+        <v>796.8</v>
+      </c>
+      <c r="D20">
+        <v>796.9</v>
+      </c>
+      <c r="E20">
+        <v>796.9</v>
+      </c>
+      <c r="F20">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21">
+        <v>153</v>
+      </c>
+      <c r="C21">
+        <v>153</v>
+      </c>
+      <c r="D21">
+        <v>153</v>
+      </c>
+      <c r="E21">
+        <v>153</v>
+      </c>
+      <c r="F21">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>7</v>
+      </c>
+      <c r="D23">
+        <v>7</v>
+      </c>
+      <c r="E23">
+        <v>7</v>
+      </c>
+      <c r="F23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>8</v>
+      </c>
+      <c r="D24">
+        <v>7</v>
+      </c>
+      <c r="E24">
+        <v>7</v>
+      </c>
+      <c r="F24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25">
+        <v>24</v>
+      </c>
+      <c r="C25">
+        <v>39</v>
+      </c>
+      <c r="D25">
+        <v>31</v>
+      </c>
+      <c r="E25">
+        <v>16</v>
+      </c>
+      <c r="F25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26">
         <v>13</v>
       </c>
-      <c r="B5">
-        <v>234</v>
-      </c>
-      <c r="C5">
-        <v>190</v>
-      </c>
-      <c r="D5">
-        <v>584</v>
-      </c>
-      <c r="E5">
-        <v>627</v>
-      </c>
-      <c r="F5">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>20</v>
-      </c>
-      <c r="D6">
+      <c r="C26">
+        <v>27</v>
+      </c>
+      <c r="D26">
+        <v>19</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" t="s">
+        <v>37</v>
+      </c>
+      <c r="F28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
         <v>42</v>
       </c>
-      <c r="E6">
+      <c r="B32">
+        <v>8</v>
+      </c>
+      <c r="C32">
+        <v>8</v>
+      </c>
+      <c r="D32">
+        <v>8</v>
+      </c>
+      <c r="E32">
+        <v>8</v>
+      </c>
+      <c r="F32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
         <v>45</v>
       </c>
-      <c r="F6">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="3">
-        <f>B5/B4</f>
-        <v>-2.7126314727850032E-4</v>
-      </c>
-      <c r="C8" s="3">
-        <f t="shared" ref="C8:F8" si="0">C5/C4</f>
-        <v>-2.2041124097328964E-4</v>
-      </c>
-      <c r="D8" s="3">
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="3">
+        <f>B16/B5</f>
+        <v>-1.3119964735019633E-3</v>
+      </c>
+      <c r="C43" s="3">
+        <f t="shared" ref="C43:F43" si="0">C16/C5</f>
+        <v>-1.6439509500197783E-3</v>
+      </c>
+      <c r="D43" s="3">
         <f t="shared" si="0"/>
-        <v>-6.6964567258683894E-4</v>
-      </c>
-      <c r="E8" s="3">
+        <v>-1.5154024716140149E-3</v>
+      </c>
+      <c r="E43" s="3">
         <f t="shared" si="0"/>
-        <v>-7.2103774235837996E-4</v>
-      </c>
-      <c r="F8" s="3">
+        <v>-1.3432875055860781E-3</v>
+      </c>
+      <c r="F43" s="3">
         <f t="shared" si="0"/>
-        <v>-2.6750062569888842E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="3">
-        <f>B6/B4</f>
-        <v>-2.5503372821055586E-5</v>
-      </c>
-      <c r="C9" s="3">
-        <f t="shared" ref="C9:F9" si="1">C6/C4</f>
-        <v>-2.3201183260346277E-5</v>
-      </c>
-      <c r="D9" s="3">
+        <v>-1.8739780540178485E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="3">
+        <f>B25/B5</f>
+        <v>-2.7840773973516463E-5</v>
+      </c>
+      <c r="C44" s="3">
+        <f t="shared" ref="C44:F44" si="1">C25/C5</f>
+        <v>-4.7177400331693413E-5</v>
+      </c>
+      <c r="D44" s="3">
         <f t="shared" si="1"/>
-        <v>-4.8159449055902798E-5</v>
-      </c>
-      <c r="E9" s="3">
+        <v>-3.8317680766749151E-5</v>
+      </c>
+      <c r="E44" s="3">
         <f t="shared" si="1"/>
-        <v>-5.1749120264955494E-5</v>
-      </c>
-      <c r="F9" s="3">
+        <v>-2.1029941379038406E-5</v>
+      </c>
+      <c r="F44" s="3">
         <f t="shared" si="1"/>
-        <v>-2.6405641163409588E-5</v>
+        <v>-6.2794271192450897E-5</v>
       </c>
     </row>
   </sheetData>
@@ -700,114 +1383,114 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3">
-        <f>-AVERAGE(Data!B8:F8)</f>
-        <v>4.2997168577917945E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+        <f>-AVERAGE(Data!B43:F43)</f>
+        <v>1.5377230909479366E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B12" s="3">
-        <f>-AVERAGE(Data!B9:F9)</f>
-        <v>3.5003753313133949E-5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+        <f>-AVERAGE(Data!B44:F44)</f>
+        <v>3.9432013528689668E-5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -816,4 +1499,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43B0B29A-4667-41A9-8548-8F5BCDA4B544}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A86E6733-3BC7-4600-9DAD-D9FF63ADAF89}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45287B9A-E4B2-46F7-9137-D38C6602A4F0}"/>
 </file>